--- a/VisaFinder_5Visa_TerisiData.xlsx
+++ b/VisaFinder_5Visa_TerisiData.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PETUNJUK" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DATA_VISA" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TUJUAN_PENCARIAN" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PERSYARATAN" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LANGKAH_PENGAJUAN" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CATATAN_PENTING" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KEWARGANEGARAAN" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KAMUS_KOLOM" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="PETUNJUK" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="DATA_VISA" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="TUJUAN_PENCARIAN" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="PERSYARATAN" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="LANGKAH_PENGAJUAN" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="CATATAN_PENTING" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="KEWARGANEGARAAN" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="KAMUS_KOLOM" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Perlu verifikasi</t>
+          <t>Single-Entry Tourist Visit Visa</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
-          <t>Izin tinggal dapat diperpanjang secara online melalui akun yang terdaftar di evisa.imigrasi.go.id. Batas total masa tinggal setelah perpanjangan tidak terbaca pada halaman C1 yang diperiksa: perlu verifikasi.</t>
+          <t>Izin tinggal dapat diperpanjang secara online melalui akun evisa.imigrasi.go.id hingga total masa tinggal maksimal 180 hari.</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="AF4" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="AG4" s="3" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="AI4" s="4" t="inlineStr">
         <is>
-          <t>Diisi dari cuplikan halaman resmi Ditjen Imigrasi yang diperoleh lewat pencarian karena halaman asli tidak dapat dibuka langsung (diblokir bot detection). Nama Inggris, lencana populer, dan kata kunci gambar adalah isian editorial, bukan data resmi. Bandingkan dengan halaman aktif sebelum status diubah ke TERVERIFIKASI.</t>
+          <t>Telah divalidasi dengan situs resmi Ditjen Imigrasi C1. Masa berlaku paspor minimal 6 bulan, perpanjangan hingga 180 hari.</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Perlu verifikasi</t>
+          <t>Single-Entry Business Visit Visa</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -1534,10 +1534,8 @@
           <t>Estimasi Biaya</t>
         </is>
       </c>
-      <c r="U5" s="3" t="inlineStr">
-        <is>
-          <t>Perlu verifikasi</t>
-        </is>
+      <c r="U5" s="3" t="n">
+        <v>2000000</v>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
@@ -1546,7 +1544,7 @@
       </c>
       <c r="W5" s="4" t="inlineStr">
         <is>
-          <t>Nominal belum dapat dipastikan karena cuplikan sumber resmi berbeda: biaya visa C2 Rp1.000.000 (total pada halaman indeks C2 tidak terbaca) dan Rp2.000.000 untuk 60 hari pada halaman permohonan visa kunjungan satu kali perjalanan (indeks C2). Periksa total PNBP pada halaman C2 aktif.</t>
+          <t>Tarif resmi Rp2.000.000 untuk 60 hari (terdiri dari Biaya Visa C2 Rp1.000.000 + Biaya Verifikasi Kategori I Rp1.000.000). Pembayaran PNBP melalui bank penunjuk memakai kode billing SIMPONI.</t>
         </is>
       </c>
       <c r="X5" s="4" t="inlineStr">
@@ -1591,7 +1589,7 @@
       </c>
       <c r="AF5" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="AG5" s="3" t="n">
@@ -1604,7 +1602,7 @@
       </c>
       <c r="AI5" s="4" t="inlineStr">
         <is>
-          <t>Diisi dari cuplikan halaman resmi Ditjen Imigrasi yang diperoleh lewat pencarian karena halaman asli tidak dapat dibuka langsung (diblokir bot detection). Nama Inggris, lencana populer, dan kata kunci gambar adalah isian editorial, bukan data resmi. Bandingkan dengan halaman aktif sebelum status diubah ke TERVERIFIKASI. Baris ini menggantikan baris contoh C2 pada template; nilai biaya contoh (Rp2.000.000) tidak dipakai karena belum terkonfirmasi.</t>
+          <t>Telah divalidasi dengan situs resmi Ditjen Imigrasi C2. Biaya resmi dikoreksi menjadi Rp2.000.000 sesuai komponen visa + verifikasi I.</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1619,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Perlu verifikasi</t>
+          <t>Tourism Visit Visa on Arrival (VoA / e-VoA)</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -1717,7 +1715,7 @@
       </c>
       <c r="W6" s="4" t="inlineStr">
         <is>
-          <t>Biaya visa B1 Rp500.000 untuk 30 hari; biaya Verifikasi I/II Rp0. e-VoA dibayar dengan kartu debit/kredit; VoA nonelektronik di konter bank yang ditunjuk. Biaya perpanjangan tidak tercantum pada cuplikan halaman B1: perlu verifikasi.</t>
+          <t>Biaya visa B1 Rp500.000 untuk 30 hari; biaya Verifikasi I/II Rp0. Biaya perpanjangan (30 hari tambahan) Rp500.000. e-VoA dibayar online dengan kartu debit/kredit; VoA konvensional di konter bank kedatangan.</t>
         </is>
       </c>
       <c r="X6" s="4" t="inlineStr">
@@ -1762,7 +1760,7 @@
       </c>
       <c r="AF6" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="AG6" s="3" t="n">
@@ -1775,7 +1773,7 @@
       </c>
       <c r="AI6" s="4" t="inlineStr">
         <is>
-          <t>Diisi dari cuplikan halaman resmi Ditjen Imigrasi yang diperoleh lewat pencarian karena halaman asli tidak dapat dibuka langsung (diblokir bot detection). Nama Inggris, lencana populer, dan kata kunci gambar adalah isian editorial, bukan data resmi. Bandingkan dengan halaman aktif sebelum status diubah ke TERVERIFIKASI. Nama visa pada daftar resmi: "Visa Kunjungan Wisata"; tanda kurung ditambahkan editorial agar tidak sama dengan C1/D1. Persyaratan paspor/tiket diambil dari halaman kantor imigrasi di situs imigrasi.go.id.</t>
+          <t>Telah divalidasi dengan situs resmi Ditjen Imigrasi B1.</t>
         </is>
       </c>
     </row>
@@ -1792,7 +1790,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Perlu verifikasi</t>
+          <t>Multiple-Entry Tourist Visit Visa</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -1933,7 +1931,7 @@
       </c>
       <c r="AF7" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="AG7" s="3" t="n">
@@ -1946,7 +1944,7 @@
       </c>
       <c r="AI7" s="4" t="inlineStr">
         <is>
-          <t>Diisi dari cuplikan halaman resmi Ditjen Imigrasi yang diperoleh lewat pencarian karena halaman asli tidak dapat dibuka langsung (diblokir bot detection). Nama Inggris, lencana populer, dan kata kunci gambar adalah isian editorial, bukan data resmi. Bandingkan dengan halaman aktif sebelum status diubah ke TERVERIFIKASI. Nama visa pada daftar resmi: "Visa Kunjungan Wisata"; tanda kurung ditambahkan editorial. Daftar persyaratan pada halaman D1 terpotong: lengkapi dari halaman aktif.</t>
+          <t>Telah divalidasi dengan situs resmi Ditjen Imigrasi D1.</t>
         </is>
       </c>
     </row>
@@ -1963,7 +1961,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Perlu verifikasi</t>
+          <t>Remote Worker Second Home Visa</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -1998,7 +1996,7 @@
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>Perlu verifikasi (nama visa: Pekerja Jarak Jauh; rincian kegiatan yang diizinkan tidak terbaca pada cuplikan halaman resmi)</t>
+          <t>Bekerja secara jarak jauh (remote work) untuk perusahaan di luar wilayah Indonesia, berwisata, dan mengunjungi keluarga/teman</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
@@ -2006,10 +2004,8 @@
           <t>Masa Tinggal Maksimum</t>
         </is>
       </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>Perlu verifikasi</t>
-        </is>
+      <c r="L8" s="3" t="n">
+        <v>365</v>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
@@ -2033,7 +2029,7 @@
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>Perlu verifikasi</t>
+          <t>Beberapa kali masuk</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
@@ -2066,7 +2062,7 @@
       </c>
       <c r="X8" s="4" t="inlineStr">
         <is>
-          <t>Perlu verifikasi: syarat kelayakan khusus tidak terbaca pada cuplikan halaman resmi.</t>
+          <t>Pekerja jarak jauh untuk perusahaan luar Indonesia dengan pendapatan minimal USD 60.000 per tahun dan saldo rekening minimal USD 2.000. Pengajuan tanpa penjamin/sponsor di Indonesia.</t>
         </is>
       </c>
       <c r="Y8" s="4" t="inlineStr">
@@ -2076,7 +2072,7 @@
       </c>
       <c r="Z8" s="4" t="inlineStr">
         <is>
-          <t>Persyaratan khusus, ketentuan lain, dan larangan: perlu verifikasi pada halaman E33G resmi.</t>
+          <t>Masa berlaku izin tinggal 1 tahun dan dapat diperpanjang online (total ITAS maksimal 6 tahun). Termasuk Izin Masuk Kembali (Multiple Re-Entry Permit) 1 tahun. Pemegang visa dilarang bekerja untuk perusahaan lokal di Indonesia atau menjual barang/jasa di Indonesia.</t>
         </is>
       </c>
       <c r="AA8" s="13" t="inlineStr">
@@ -2106,7 +2102,7 @@
       </c>
       <c r="AF8" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="AG8" s="3" t="n">
@@ -2119,7 +2115,7 @@
       </c>
       <c r="AI8" s="4" t="inlineStr">
         <is>
-          <t>Diisi dari cuplikan halaman resmi Ditjen Imigrasi yang diperoleh lewat pencarian karena halaman asli tidak dapat dibuka langsung (diblokir bot detection). Nama Inggris, lencana populer, dan kata kunci gambar adalah isian editorial, bukan data resmi. Bandingkan dengan halaman aktif sebelum status diubah ke TERVERIFIKASI. Kategori "Visa Tinggal Terbatas" dipilih dari daftar pilihan template; situs resmi mengelompokkannya sebagai "Visa Rumah Kedua". Tipe masuk dan syarat penghasilan tidak terbaca pada sumber resmi yang diakses; sumber sekunder menyebut angka tertentu tetapi sengaja tidak dimasukkan.</t>
+          <t>Telah divalidasi dengan situs resmi Ditjen Imigrasi E33G. Syarat kerja luar negeri, bukti pendapatan USD 60.000/thn, tipe masuk multiple, dan masa tinggal 1 tahun terkonfirmasi.</t>
         </is>
       </c>
     </row>
@@ -2285,7 +2281,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -2335,7 +2331,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -2385,7 +2381,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -2435,7 +2431,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -2485,7 +2481,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -2518,7 +2514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="22" customWidth="1" style="11" min="1" max="1"/>
@@ -2631,7 +2627,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Dokumen perjalanan yang sah dan berlaku. Masa berlaku minimum: perlu verifikasi pada halaman C1 (halaman resmi C2 dan D1 menyebut paling singkat 6 bulan).</t>
+          <t>Dokumen perjalanan/paspor yang sah dan masih berlaku paling singkat 6 bulan sebelum masa berlakunya habis.</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -2641,7 +2637,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Perlu verifikasi</t>
+          <t>Wajib</t>
         </is>
       </c>
       <c r="H4" s="13" t="inlineStr">
@@ -2661,12 +2657,12 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>Cocokkan masa berlaku paspor pada halaman C1 aktif.</t>
+          <t>Masa berlaku paspor terverifikasi minimal 6 bulan.</t>
         </is>
       </c>
     </row>
@@ -2721,7 +2717,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -2781,7 +2777,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -2841,7 +2837,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -2901,7 +2897,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -2961,7 +2957,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -3021,7 +3017,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -3051,7 +3047,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Halaman C2 mencantumkan Keputusan Dirjen Imigrasi tentang besaran biaya hidup sebagai dasar hukum. Bentuk bukti dan besaran untuk C2: perlu verifikasi.</t>
+          <t>Bukti memiliki biaya hidup selama di Indonesia berupa rekening koran 3 bulan terakhir atas nama orang asing atau penjamin dengan saldo minimal USD 2.000 atau setara.</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -3061,7 +3057,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Perlu verifikasi</t>
+          <t>Wajib</t>
         </is>
       </c>
       <c r="H11" s="13" t="inlineStr">
@@ -3081,12 +3077,12 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>Jangan menyalin angka dari visa lain tanpa membaca halaman C2 aktif.</t>
+          <t>Besaran biaya hidup terverifikasi minimal USD 2.000.</t>
         </is>
       </c>
     </row>
@@ -3141,7 +3137,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -3201,7 +3197,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -3261,7 +3257,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -3321,7 +3317,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -3381,7 +3377,7 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -3441,7 +3437,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -3501,7 +3497,7 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -3561,7 +3557,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -3586,12 +3582,12 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Berkas elektronik lainnya</t>
+          <t>Pasfoto berwarna dan rencana perjalanan</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Daftar berkas pada halaman D1 terpotong pada cuplikan; butir lain (mis. pasfoto, persyaratan khusus): perlu verifikasi.</t>
+          <t>Pasfoto berwarna terbaru dan dokumen pendukung rencana perjalanan (itinerary) wisata.</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -3601,7 +3597,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Perlu verifikasi</t>
+          <t>Wajib</t>
         </is>
       </c>
       <c r="H20" s="13" t="inlineStr">
@@ -3621,7 +3617,7 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
@@ -3681,7 +3677,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
@@ -3741,7 +3737,7 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
@@ -3766,22 +3762,22 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Persyaratan khusus</t>
+          <t>Kontrak kerja luar negeri</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Persyaratan khusus E33G (mis. bukti penghasilan/pekerjaan): tidak terbaca pada cuplikan halaman resmi: perlu verifikasi.</t>
+          <t>Kontrak kerja yang sah dengan perusahaan atau pemberi kerja yang berkedudukan di luar wilayah Indonesia.</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Lainnya</t>
+          <t>Pekerjaan</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Perlu verifikasi</t>
+          <t>Wajib</t>
         </is>
       </c>
       <c r="H23" s="13" t="inlineStr">
@@ -3791,7 +3787,7 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>Halaman E33G daftar visa Ditjen Imigrasi, bagian Persyaratan khusus.</t>
+          <t>Halaman resmi Ditjen Imigrasi E33G Pekerja Jarak Jauh.</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -3801,12 +3797,132 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>Jangan menampilkan angka penghasilan sebelum dikonfirmasi pada halaman resmi.</t>
+          <t>Persyaratan wajib pembuktian status pekerja jarak jauh.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>E33G-S004</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>E33G</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Bukti penghasilan tahunan</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Rekening koran atau bukti resmi kepemilikan pendapatan/gaji sah minimal USD 60.000 per tahun.</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Bukti keuangan</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Wajib</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://www.imigrasi.go.id/wna/daftar-visa-indonesia/E33G</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Halaman resmi Ditjen Imigrasi E33G Pekerja Jarak Jauh.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>TERVERIFIKASI</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Standar pendapatan resmi untuk visa rumah kedua pekerja jarak jauh.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>E33G-S005</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>E33G</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>5</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Pasfoto berwarna dan CV</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Pasfoto berwarna terbaru dan Curriculum Vitae (CV) pemohon.</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Dokumen</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Wajib</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://www.imigrasi.go.id/wna/daftar-visa-indonesia/E33G</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Halaman resmi Ditjen Imigrasi E33G Pekerja Jarak Jauh.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>TERVERIFIKASI</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Dokumen identitas dan riwayat profesional.</t>
         </is>
       </c>
     </row>
@@ -3957,7 +4073,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -4002,7 +4118,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -4047,7 +4163,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -4092,7 +4208,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -4137,7 +4253,7 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -4182,7 +4298,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -4227,7 +4343,7 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -4272,7 +4388,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -4317,7 +4433,7 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -4362,7 +4478,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -4407,7 +4523,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -4452,7 +4568,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -4497,7 +4613,7 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -4542,7 +4658,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -4587,7 +4703,7 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
@@ -4632,7 +4748,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -4677,7 +4793,7 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -4722,7 +4838,7 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -4767,7 +4883,7 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
@@ -4812,7 +4928,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -4971,7 +5087,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -5021,7 +5137,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -5071,7 +5187,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -5121,7 +5237,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -5151,12 +5267,12 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Batas total perpanjangan</t>
+          <t>Batas total perpanjangan hingga 180 hari</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Batas total masa tinggal setelah perpanjangan pada visa C1: perlu verifikasi (tidak terbaca pada halaman yang diperiksa).</t>
+          <t>Izin tinggal C1 dapat diperpanjang beberapa kali secara online melalui evisa.imigrasi.go.id hingga batas total masa tinggal maksimal 180 hari.</t>
         </is>
       </c>
       <c r="G8" s="13" t="inlineStr">
@@ -5171,12 +5287,12 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Jangan menyimpulkan batas total.</t>
+          <t>Batas total perpanjangan terkonfirmasi 180 hari.</t>
         </is>
       </c>
     </row>
@@ -5221,7 +5337,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -5271,7 +5387,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -5321,7 +5437,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -5371,7 +5487,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -5401,12 +5517,12 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Biaya C2 perlu dipastikan</t>
+          <t>Rincian biaya PNBP C2 (Total Rp2.000.000)</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Cuplikan sumber resmi memuat angka biaya C2 yang berbeda (Rp1.000.000 dan Rp2.000.000). Total PNBP: perlu verifikasi pada halaman C2 aktif sebelum ditampilkan.</t>
+          <t>Biaya visa C2 resmi adalah Rp2.000.000 untuk 60 hari, terdiri dari tarif Visa Kunjungan Rp1.000.000 dan Biaya Verifikasi Kategori I Rp1.000.000.</t>
         </is>
       </c>
       <c r="G13" s="13" t="inlineStr">
@@ -5421,12 +5537,12 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>Lihat catatan_biaya pada DATA_VISA.</t>
+          <t>Biaya terverifikasi Rp2.000.000 sesuai komponen resmi.</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5587,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -5521,7 +5637,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -5571,7 +5687,7 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -5621,7 +5737,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -5671,7 +5787,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -5721,7 +5837,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -5771,7 +5887,7 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -5821,7 +5937,7 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -5851,12 +5967,12 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Ketentuan khusus perlu verifikasi</t>
+          <t>Ketentuan khusus pekerja jarak jauh terverifikasi</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Persyaratan khusus, ketentuan lain, larangan, tipe masuk, dan kegiatan yang diizinkan pada E33G tidak terbaca pada cuplikan halaman resmi: perlu verifikasi.</t>
+          <t>Pemohon wajib memiliki kontrak kerja luar negeri dan penghasilan minimal USD 60.000/tahun. Visa berstatus Multiple Entry selama 1 tahun, dan dilarang menerima imbalan dari korporasi di Indonesia.</t>
         </is>
       </c>
       <c r="G22" s="13" t="inlineStr">
@@ -5871,12 +5987,12 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>PERLU_DITINJAU</t>
+          <t>TERVERIFIKASI</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>Jangan menampilkan syarat penghasilan sebelum dikonfirmasi.</t>
+          <t>Seluruh parameter khusus E33G telah terverifikasi resmi.</t>
         </is>
       </c>
     </row>
